--- a/Lab-trails/2026-04-29-CattleSlurryRetry-slurry.xlsx
+++ b/Lab-trails/2026-04-29-CattleSlurryRetry-slurry.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-29-cattle-slurry-retrail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A20895-B8B7-410F-82FF-C710C220D644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778FF9C9-7F32-4D8D-AA0D-6CE5DCEA7991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
     <sheet name="DM" sheetId="2" r:id="rId2"/>
     <sheet name="pH" sheetId="3" r:id="rId3"/>
+    <sheet name="TAN-App-rate" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -222,14 +223,73 @@
   <si>
     <t>pH  (after acidification)</t>
   </si>
+  <si>
+    <t xml:space="preserve">ID </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NH4-N [g/L] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stdev</t>
+    </r>
+  </si>
+  <si>
+    <t>NH4-N [kg/L]</t>
+  </si>
+  <si>
+    <t>NH4-N stdev [kg/L]</t>
+  </si>
+  <si>
+    <t>slurry target[g or mL]</t>
+  </si>
+  <si>
+    <t>slurry target [kg or L]</t>
+  </si>
+  <si>
+    <t>surface area [cm2]</t>
+  </si>
+  <si>
+    <t>surface area [ha]</t>
+  </si>
+  <si>
+    <t>Slurry app [L / ha]</t>
+  </si>
+  <si>
+    <t>NH4-N app mean [kg/ha]</t>
+  </si>
+  <si>
+    <t>NH4-N app stdev [kg/ha]</t>
+  </si>
+  <si>
+    <t>Cattle slurry untreated</t>
+  </si>
+  <si>
+    <t>Ammonium carbonate std untreated</t>
+  </si>
+  <si>
+    <t>Cattle slurry AA</t>
+  </si>
+  <si>
+    <t>Cattle slurry SA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -268,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -277,6 +337,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1310,4 +1371,249 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E78351-1B9D-4453-B268-552ADCB91111}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <f>B2*10^-3</f>
+        <v>1.89E-3</v>
+      </c>
+      <c r="E2">
+        <f>C2*10^-3</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <f>F2*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H2">
+        <v>28.27</v>
+      </c>
+      <c r="I2">
+        <f>H2*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J2" s="5">
+        <f>G2/I2</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K2" s="6">
+        <f>D2*J2</f>
+        <v>13.371064732932437</v>
+      </c>
+      <c r="L2" s="6">
+        <f>J2*E2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="3">
+        <f>TAN!G4</f>
+        <v>2.0501118881992579</v>
+      </c>
+      <c r="C3" s="3">
+        <f>TAN!H4</f>
+        <v>0.11175002139738323</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D4" si="0">B3*10^-3</f>
+        <v>2.0501118881992579E-3</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E4" si="1">C3*10^-3</f>
+        <v>1.1175002139738323E-4</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G4" si="2">F3*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H3">
+        <v>28.27</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I4" si="3">H3*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J3" s="5">
+        <f t="shared" ref="J3:J4" si="4">G3/I3</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K3" s="6">
+        <f t="shared" ref="K3:K4" si="5">D3*J3</f>
+        <v>14.50379828934742</v>
+      </c>
+      <c r="L3" s="6">
+        <f t="shared" ref="L3:L4" si="6">J3*E3</f>
+        <v>0.79059088360370167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="3">
+        <f>TAN!G7</f>
+        <v>2.0301157672396664</v>
+      </c>
+      <c r="C4" s="3">
+        <f>TAN!H7</f>
+        <v>5.0805705133357561E-2</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>2.0301157672396662E-3</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>5.0805705133357559E-5</v>
+      </c>
+      <c r="F4" s="6">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="2"/>
+        <v>2E-3</v>
+      </c>
+      <c r="H4">
+        <v>28.27</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="3"/>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="4"/>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" si="5"/>
+        <v>14.362332983655225</v>
+      </c>
+      <c r="L4" s="6">
+        <f t="shared" si="6"/>
+        <v>0.35943194293142949</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3">
+        <f>TAN!G13</f>
+        <v>3.5846328082546735</v>
+      </c>
+      <c r="C5" s="3">
+        <f>TAN!H13</f>
+        <v>0.18074382573656025</v>
+      </c>
+      <c r="D5" s="1">
+        <f>B5*10^-3</f>
+        <v>3.5846328082546736E-3</v>
+      </c>
+      <c r="E5">
+        <f>C5*10^-3</f>
+        <v>1.8074382573656026E-4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <f>F5*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H5">
+        <v>28.27</v>
+      </c>
+      <c r="I5">
+        <f>H5*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J5" s="5">
+        <f>G5/I5</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K5" s="6">
+        <f>D5*J5</f>
+        <v>25.359977419559062</v>
+      </c>
+      <c r="L5" s="6">
+        <f>J5*E5</f>
+        <v>1.2786970338631782</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>